--- a/通信协议.xlsx
+++ b/通信协议.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\00_project\3_csharp\UniversalHost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8FB9C7-B50D-4462-AA99-4E2E488C32C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DF043F-C3E3-428F-B3B1-695651FEC7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7770" yWindow="2290" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3320" yWindow="1820" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IAP" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="211">
   <si>
     <t>PC发送</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,10 +204,6 @@
   </si>
   <si>
     <t>byte4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对于逐帧写入的设备，不需要等待擦除和烧录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -856,6 +852,14 @@
   </si>
   <si>
     <t>一帧字节数L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对于逐帧写入的设备，在这里等待擦除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对于逐帧写入的设备，不需要在这里等待擦除和烧录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1238,7 +1242,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -1246,7 +1250,7 @@
         <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1295,10 +1299,10 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" t="s">
         <v>52</v>
-      </c>
-      <c r="G4" t="s">
-        <v>53</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -1356,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -1377,13 +1381,13 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K6" t="s">
+        <v>207</v>
+      </c>
+      <c r="L6" t="s">
         <v>208</v>
-      </c>
-      <c r="L6" t="s">
-        <v>209</v>
       </c>
       <c r="M6" t="s">
         <v>9</v>
@@ -1406,7 +1410,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>
@@ -1432,10 +1436,10 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
         <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -1526,13 +1530,13 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -1544,7 +1548,7 @@
         <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N11" t="s">
         <v>38</v>
@@ -1605,6 +1609,9 @@
       <c r="K12" t="s">
         <v>10</v>
       </c>
+      <c r="L12" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="J13" s="2"/>
@@ -1620,10 +1627,10 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
         <v>52</v>
-      </c>
-      <c r="G15" t="s">
-        <v>53</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -1687,14 +1694,14 @@
         <v>17</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -1772,10 +1779,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" t="s">
         <v>52</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1853,7 +1860,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -1915,7 +1922,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
@@ -1964,7 +1971,7 @@
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
@@ -1996,7 +2003,7 @@
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
@@ -2028,7 +2035,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H28" t="s">
         <v>5</v>
@@ -2060,7 +2067,7 @@
         <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H30" t="s">
         <v>5</v>
@@ -2078,7 +2085,7 @@
         <v>10</v>
       </c>
       <c r="M30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -2095,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
@@ -2127,7 +2134,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H33" t="s">
         <v>5</v>
@@ -2147,7 +2154,7 @@
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -2159,13 +2166,13 @@
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H34" t="s">
         <v>5</v>
       </c>
       <c r="I34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J34" t="s">
         <v>5</v>
@@ -2179,7 +2186,7 @@
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -2191,13 +2198,13 @@
         <v>5</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H35" t="s">
         <v>5</v>
       </c>
       <c r="I35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J35" t="s">
         <v>5</v>
@@ -2225,373 +2232,373 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J2" t="s">
         <v>164</v>
-      </c>
-      <c r="J2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
         <v>115</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>116</v>
       </c>
-      <c r="D21" t="s">
+      <c r="G21" t="s">
         <v>117</v>
-      </c>
-      <c r="G21" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" t="s">
         <v>119</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>120</v>
       </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
         <v>121</v>
-      </c>
-      <c r="G22" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
         <v>123</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
         <v>124</v>
       </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>125</v>
-      </c>
-      <c r="G23" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" t="s">
         <v>127</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
         <v>128</v>
       </c>
-      <c r="D24" t="s">
+      <c r="G24" t="s">
         <v>129</v>
-      </c>
-      <c r="G24" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
         <v>131</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>132</v>
       </c>
-      <c r="D25" t="s">
+      <c r="G25" t="s">
         <v>133</v>
-      </c>
-      <c r="G25" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
         <v>135</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
         <v>136</v>
       </c>
-      <c r="D26" t="s">
+      <c r="G26" t="s">
         <v>137</v>
-      </c>
-      <c r="G26" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
         <v>139</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>140</v>
       </c>
-      <c r="D27" t="s">
+      <c r="G27" t="s">
         <v>141</v>
-      </c>
-      <c r="G27" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" t="s">
         <v>143</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
         <v>144</v>
       </c>
-      <c r="D28" t="s">
+      <c r="G28" t="s">
         <v>145</v>
-      </c>
-      <c r="G28" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" t="s">
         <v>147</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
         <v>148</v>
       </c>
-      <c r="D29" t="s">
+      <c r="G29" t="s">
         <v>149</v>
-      </c>
-      <c r="G29" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" t="s">
         <v>151</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
         <v>152</v>
       </c>
-      <c r="D30" t="s">
+      <c r="G30" t="s">
         <v>153</v>
-      </c>
-      <c r="G30" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s">
         <v>155</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
         <v>156</v>
       </c>
-      <c r="D31" t="s">
+      <c r="G31" t="s">
         <v>157</v>
-      </c>
-      <c r="G31" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" t="s">
         <v>159</v>
       </c>
-      <c r="B32" t="s">
+      <c r="D32" t="s">
         <v>160</v>
       </c>
-      <c r="D32" t="s">
+      <c r="G32" t="s">
         <v>161</v>
-      </c>
-      <c r="G32" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2613,173 +2620,173 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" t="s">
         <v>169</v>
       </c>
-      <c r="B1" t="s">
-        <v>170</v>
-      </c>
       <c r="C1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" t="s">
         <v>166</v>
       </c>
-      <c r="B2" t="s">
-        <v>167</v>
-      </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D3" t="s">
-        <v>174</v>
-      </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" t="s">
         <v>177</v>
-      </c>
-      <c r="C4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" t="s">
         <v>179</v>
-      </c>
-      <c r="C5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" t="s">
         <v>181</v>
-      </c>
-      <c r="C6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E6" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" t="s">
         <v>183</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>184</v>
-      </c>
-      <c r="E7" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" t="s">
         <v>186</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" t="s">
         <v>187</v>
       </c>
-      <c r="C10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" t="s">
-        <v>188</v>
-      </c>
       <c r="E10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" t="s">
         <v>189</v>
-      </c>
-      <c r="C11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" t="s">
         <v>192</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>193</v>
-      </c>
-      <c r="C14" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" t="s">
         <v>195</v>
-      </c>
-      <c r="C15" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">

--- a/通信协议.xlsx
+++ b/通信协议.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\00_project\3_csharp\UniversalHost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DF043F-C3E3-428F-B3B1-695651FEC7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191F468A-4223-4F26-B461-0F271ECE8638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3320" yWindow="1820" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="3120" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IAP" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="247">
   <si>
     <t>PC发送</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -860,6 +860,126 @@
   </si>
   <si>
     <t>对于逐帧写入的设备，不需要在这里等待擦除和烧录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图表区域scottplot快捷键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按键</t>
+  </si>
+  <si>
+    <t>默认操作</t>
+  </si>
+  <si>
+    <t>← ↑ → ↓</t>
+  </si>
+  <si>
+    <t>向对应方向平移图表</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>自动调整坐标轴范围（AutoScale）</t>
+  </si>
+  <si>
+    <t>Shift 或 Alt + 方向键</t>
+  </si>
+  <si>
+    <t>Ctrl + 方向键</t>
+  </si>
+  <si>
+    <t>改变平移步长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放图表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作</t>
+  </si>
+  <si>
+    <t>默认功能</t>
+  </si>
+  <si>
+    <t>左键拖动</t>
+  </si>
+  <si>
+    <t>平移</t>
+  </si>
+  <si>
+    <t>右键拖动</t>
+  </si>
+  <si>
+    <t>缩放</t>
+  </si>
+  <si>
+    <t>滚轮</t>
+  </si>
+  <si>
+    <t>以鼠标位置为中心缩放</t>
+  </si>
+  <si>
+    <t>中键单击</t>
+  </si>
+  <si>
+    <t>自动调整坐标轴范围</t>
+  </si>
+  <si>
+    <t>中键拖动</t>
+  </si>
+  <si>
+    <t>框选区域并放大</t>
+  </si>
+  <si>
+    <t>右键单击</t>
+  </si>
+  <si>
+    <t>打开右键菜单</t>
+  </si>
+  <si>
+    <t>左键双击</t>
+  </si>
+  <si>
+    <t>运行 Benchmark</t>
+  </si>
+  <si>
+    <t>Alt + 左键拖动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ctrl + 滚轮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X轴缩放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ctrl + 左键拖动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X轴平移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shift + 左键拖动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shift + 滚轮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y轴平移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y轴缩放</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2227,10 +2347,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D0F226-982F-48E5-8704-E896A0BD1D42}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" customWidth="1"/>
+    <col min="15" max="15" width="20.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>63</v>
       </c>
@@ -2244,7 +2369,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -2270,7 +2395,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -2296,7 +2421,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -2316,7 +2441,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -2330,7 +2455,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -2344,7 +2469,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>86</v>
       </c>
@@ -2352,7 +2477,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -2360,7 +2485,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -2370,8 +2495,17 @@
       <c r="F10" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>211</v>
+      </c>
+      <c r="N10" t="s">
+        <v>222</v>
+      </c>
+      <c r="O10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -2381,8 +2515,20 @@
       <c r="D11" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>212</v>
+      </c>
+      <c r="J11" t="s">
+        <v>213</v>
+      </c>
+      <c r="N11" t="s">
+        <v>224</v>
+      </c>
+      <c r="O11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>75</v>
       </c>
@@ -2392,48 +2538,132 @@
       <c r="D12" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J12" t="s">
+        <v>215</v>
+      </c>
+      <c r="N12" t="s">
+        <v>226</v>
+      </c>
+      <c r="O12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>76</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>218</v>
+      </c>
+      <c r="J13" t="s">
+        <v>220</v>
+      </c>
+      <c r="N13" t="s">
+        <v>228</v>
+      </c>
+      <c r="O13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>77</v>
       </c>
       <c r="B14" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>219</v>
+      </c>
+      <c r="J14" t="s">
+        <v>221</v>
+      </c>
+      <c r="N14" t="s">
+        <v>230</v>
+      </c>
+      <c r="O14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I15" t="s">
+        <v>216</v>
+      </c>
+      <c r="J15" t="s">
+        <v>217</v>
+      </c>
+      <c r="N15" t="s">
+        <v>232</v>
+      </c>
+      <c r="O15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>78</v>
       </c>
       <c r="B16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="N16" t="s">
+        <v>238</v>
+      </c>
+      <c r="O16" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>79</v>
       </c>
       <c r="B17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="N17" t="s">
+        <v>234</v>
+      </c>
+      <c r="O17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N18" t="s">
+        <v>236</v>
+      </c>
+      <c r="O18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N19" t="s">
+        <v>241</v>
+      </c>
+      <c r="O19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N20" t="s">
+        <v>239</v>
+      </c>
+      <c r="O20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -2446,8 +2676,14 @@
       <c r="G21" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="N21" t="s">
+        <v>243</v>
+      </c>
+      <c r="O21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>118</v>
       </c>
@@ -2460,8 +2696,14 @@
       <c r="G22" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="N22" t="s">
+        <v>244</v>
+      </c>
+      <c r="O22" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>122</v>
       </c>
@@ -2475,7 +2717,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>126</v>
       </c>
@@ -2489,7 +2731,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -2503,7 +2745,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -2517,7 +2759,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2531,7 +2773,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -2545,7 +2787,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>146</v>
       </c>
@@ -2559,7 +2801,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>150</v>
       </c>
@@ -2573,7 +2815,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>154</v>
       </c>
@@ -2587,7 +2829,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>158</v>
       </c>
